--- a/artfynd/A 911-2024 artfynd.xlsx
+++ b/artfynd/A 911-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 911-2024 artfynd.xlsx
+++ b/artfynd/A 911-2024 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>114463743</v>
+        <v>114466576</v>
       </c>
       <c r="B2" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>4217</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,27 +708,26 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 911, Hjulby, Sm</t>
+          <t>Hjulby_A911-2024, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589317</v>
+        <v>589371</v>
       </c>
       <c r="R2" t="n">
-        <v>6424416</v>
+        <v>6424280</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -771,55 +765,51 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Larsgunnar Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
+          <t>Larsgunnar Nilsson, Magnus Kasselstrand, Ingvor Kasselstrand, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>114466576</v>
+        <v>114463743</v>
       </c>
       <c r="B3" t="n">
-        <v>90726</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4217</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -827,26 +817,27 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Hjulby_A911-2024, Sm</t>
+          <t>A 911, Hjulby, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589371</v>
+        <v>589317</v>
       </c>
       <c r="R3" t="n">
-        <v>6424280</v>
+        <v>6424416</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -884,19 +875,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gunilla Nilsson, Ingvor Kasselstrand, Magnus Kasselstrand, Larsgunnar Nilsson</t>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand, Larsgunnar Nilsson, Gunilla Nilsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
